--- a/data/pierce_trends_monthly.xlsx
+++ b/data/pierce_trends_monthly.xlsx
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -418,37 +430,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>24mx</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>xlmoto</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sledstore</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -458,11 +470,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -472,11 +484,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -486,11 +498,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -500,11 +512,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
@@ -514,11 +526,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
@@ -528,11 +540,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -542,11 +554,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
@@ -556,11 +568,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
@@ -570,11 +582,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -584,11 +596,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -598,25 +610,25 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -626,25 +638,25 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
@@ -654,7 +666,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
@@ -668,11 +680,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
@@ -682,25 +694,25 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C20" t="n">
         <v>12</v>
@@ -710,7 +722,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
@@ -724,11 +736,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" t="n">
         <v>10</v>
@@ -738,11 +750,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C23" t="n">
         <v>9</v>
@@ -752,7 +764,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
@@ -766,11 +778,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C25" t="n">
         <v>12</v>
@@ -780,95 +792,95 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="n">
         <v>25</v>
@@ -878,25 +890,25 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n">
         <v>18</v>
@@ -906,53 +918,53 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B36" t="n">
         <v>83</v>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B37" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C38" t="n">
         <v>19</v>
@@ -962,53 +974,53 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B39" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D39" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B40" t="n">
         <v>68</v>
       </c>
       <c r="C40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C41" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" t="n">
         <v>33</v>
@@ -1018,25 +1030,25 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
+        <v>66</v>
+      </c>
+      <c r="C43" t="n">
+        <v>31</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B44" t="n">
         <v>70</v>
-      </c>
-      <c r="C43" t="n">
-        <v>32</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43677</v>
-      </c>
-      <c r="B44" t="n">
-        <v>73</v>
       </c>
       <c r="C44" t="n">
         <v>29</v>
@@ -1046,39 +1058,39 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C45" t="n">
         <v>25</v>
       </c>
       <c r="D45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>43738</v>
+      </c>
+      <c r="B46" t="n">
+        <v>68</v>
+      </c>
+      <c r="C46" t="n">
+        <v>24</v>
+      </c>
+      <c r="D46" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>43738</v>
-      </c>
-      <c r="B46" t="n">
-        <v>66</v>
-      </c>
-      <c r="C46" t="n">
-        <v>25</v>
-      </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C47" t="n">
         <v>22</v>
@@ -1088,11 +1100,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C48" t="n">
         <v>35</v>
@@ -1102,11 +1114,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C49" t="n">
         <v>29</v>
@@ -1116,21 +1128,21 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C50" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
@@ -1140,15 +1152,15 @@
         <v>31</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" t="n">
         <v>30</v>
@@ -1158,21 +1170,21 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C53" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D53" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
@@ -1186,77 +1198,77 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C56" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C57" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
         <v>58</v>
       </c>
       <c r="C58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
         <v>63</v>
       </c>
       <c r="C59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
@@ -1266,11 +1278,11 @@
         <v>37</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
@@ -1284,25 +1296,25 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D62" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" t="n">
         <v>28</v>
@@ -1312,53 +1324,53 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B64" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D64" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C65" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D65" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" t="n">
         <v>30</v>
@@ -1368,67 +1380,67 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C68" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C69" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D69" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B71" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C71" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D71" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -1438,95 +1450,95 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D74" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C75" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D75" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C76" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D76" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C77" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D77" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C78" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C79" t="n">
         <v>35</v>
@@ -1536,53 +1548,53 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B80" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C80" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D82" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C83" t="n">
         <v>18</v>
@@ -1592,63 +1604,63 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D84" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D85" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C86" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D86" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C87" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D87" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
@@ -1662,77 +1674,77 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C89" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D89" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C90" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
         <v>52</v>
       </c>
       <c r="C91" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C93" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
@@ -1746,11 +1758,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C95" t="n">
         <v>14</v>
@@ -1760,53 +1772,53 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C96" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D96" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C97" t="n">
         <v>13</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C98" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D98" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C99" t="n">
         <v>18</v>
@@ -1816,25 +1828,25 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C100" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D100" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C101" t="n">
         <v>24</v>
@@ -1844,11 +1856,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C102" t="n">
         <v>25</v>
@@ -1858,11 +1870,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C103" t="n">
         <v>22</v>
@@ -1872,53 +1884,53 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C104" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C105" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C106" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C107" t="n">
         <v>12</v>
@@ -1928,35 +1940,35 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C108" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D108" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B109" t="n">
         <v>40</v>
       </c>
       <c r="C109" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D109" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B110" t="n">
@@ -1970,11 +1982,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C111" t="n">
         <v>14</v>
@@ -1984,49 +1996,49 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D112" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C113" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C114" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B115" t="n">
@@ -2036,15 +2048,15 @@
         <v>19</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C116" t="n">
         <v>18</v>
@@ -2054,11 +2066,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C117" t="n">
         <v>17</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C118" t="n">
         <v>13</v>
@@ -2082,39 +2094,39 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C119" t="n">
         <v>10</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C120" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C121" t="n">
         <v>12</v>
@@ -2124,11 +2136,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C122" t="n">
         <v>10</v>
@@ -2138,25 +2150,25 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C123" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D123" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C124" t="n">
         <v>21</v>
@@ -2166,16 +2178,86 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B125" t="n">
+        <v>36</v>
+      </c>
+      <c r="C125" t="n">
+        <v>21</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>41</v>
+      </c>
+      <c r="C126" t="n">
+        <v>20</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B127" t="n">
+        <v>41</v>
+      </c>
+      <c r="C127" t="n">
+        <v>19</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B128" t="n">
         <v>42</v>
       </c>
-      <c r="C125" t="n">
-        <v>20</v>
-      </c>
-      <c r="D125" t="n">
+      <c r="C128" t="n">
+        <v>16</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B129" t="n">
+        <v>40</v>
+      </c>
+      <c r="C129" t="n">
+        <v>11</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B130" t="n">
+        <v>33</v>
+      </c>
+      <c r="C130" t="n">
+        <v>10</v>
+      </c>
+      <c r="D130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2190,93 +2272,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>24mx</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>xlmoto</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sledstore</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
+        <v>43</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>42490</v>
+      </c>
+      <c r="B5" t="n">
         <v>40</v>
       </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>42490</v>
-      </c>
-      <c r="B5" t="n">
-        <v>43</v>
-      </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n">
         <v>14</v>
@@ -2286,245 +2368,245 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
         <v>49</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C18" t="n">
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C20" t="n">
         <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
         <v>51</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" t="n">
         <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C23" t="n">
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
@@ -2538,161 +2620,161 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
+        <v>55</v>
+      </c>
+      <c r="C28" t="n">
+        <v>45</v>
+      </c>
+      <c r="D28" t="n">
         <v>66</v>
       </c>
-      <c r="C28" t="n">
-        <v>47</v>
-      </c>
-      <c r="D28" t="n">
-        <v>62</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C29" t="n">
         <v>63</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D30" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C35" t="n">
         <v>35</v>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B36" t="n">
@@ -2702,141 +2784,141 @@
         <v>44</v>
       </c>
       <c r="D36" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B37" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C37" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C38" t="n">
+        <v>42</v>
+      </c>
+      <c r="D38" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>43524</v>
+      </c>
+      <c r="B39" t="n">
+        <v>53</v>
+      </c>
+      <c r="C39" t="n">
         <v>43</v>
       </c>
-      <c r="D38" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>43524</v>
-      </c>
-      <c r="B39" t="n">
-        <v>51</v>
-      </c>
-      <c r="C39" t="n">
-        <v>44</v>
-      </c>
       <c r="D39" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B40" t="n">
         <v>68</v>
       </c>
       <c r="C40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D40" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C41" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" t="n">
         <v>73</v>
       </c>
       <c r="D42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
+        <v>66</v>
+      </c>
+      <c r="C43" t="n">
+        <v>69</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B44" t="n">
         <v>70</v>
       </c>
-      <c r="C43" t="n">
-        <v>71</v>
-      </c>
-      <c r="D43" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43677</v>
-      </c>
-      <c r="B44" t="n">
-        <v>73</v>
-      </c>
       <c r="C44" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D44" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C45" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D45" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C46" t="n">
         <v>54</v>
@@ -2846,175 +2928,175 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C48" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D48" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C49" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D49" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C50" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
         <v>68</v>
       </c>
       <c r="C51" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D51" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D52" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C53" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D53" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
         <v>89</v>
       </c>
       <c r="C54" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C55" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D55" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C56" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D56" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C57" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D57" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
         <v>58</v>
       </c>
       <c r="C58" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
@@ -3024,25 +3106,25 @@
         <v>46</v>
       </c>
       <c r="D59" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
         <v>100</v>
       </c>
       <c r="C60" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D60" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
@@ -3052,375 +3134,375 @@
         <v>56</v>
       </c>
       <c r="D61" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C62" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D62" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" t="n">
         <v>63</v>
       </c>
       <c r="D63" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B64" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D64" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C65" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D66" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C68" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D68" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C69" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C70" t="n">
         <v>48</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B71" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C72" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D72" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C73" t="n">
         <v>37</v>
       </c>
       <c r="D73" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B74" t="n">
         <v>59</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="B74" t="n">
-        <v>60</v>
       </c>
       <c r="C74" t="n">
         <v>55</v>
       </c>
       <c r="D74" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C75" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D75" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C76" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D76" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C77" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C78" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D78" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C79" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B80" t="n">
+        <v>60</v>
+      </c>
+      <c r="C80" t="n">
         <v>65</v>
-      </c>
-      <c r="C80" t="n">
-        <v>68</v>
       </c>
       <c r="D80" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C81" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D81" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
+        <v>50</v>
+      </c>
+      <c r="C82" t="n">
         <v>47</v>
-      </c>
-      <c r="C82" t="n">
-        <v>48</v>
       </c>
       <c r="D82" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C83" t="n">
+        <v>39</v>
+      </c>
+      <c r="D83" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B84" t="n">
+        <v>72</v>
+      </c>
+      <c r="C84" t="n">
+        <v>58</v>
+      </c>
+      <c r="D84" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B85" t="n">
+        <v>48</v>
+      </c>
+      <c r="C85" t="n">
+        <v>43</v>
+      </c>
+      <c r="D85" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B86" t="n">
         <v>40</v>
       </c>
-      <c r="D83" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B84" t="n">
-        <v>75</v>
-      </c>
-      <c r="C84" t="n">
-        <v>59</v>
-      </c>
-      <c r="D84" t="n">
+      <c r="C86" t="n">
+        <v>43</v>
+      </c>
+      <c r="D86" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B87" t="n">
+        <v>40</v>
+      </c>
+      <c r="C87" t="n">
         <v>48</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B85" t="n">
-        <v>52</v>
-      </c>
-      <c r="C85" t="n">
-        <v>44</v>
-      </c>
-      <c r="D85" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>44957</v>
-      </c>
-      <c r="B86" t="n">
+      <c r="D87" t="n">
         <v>42</v>
       </c>
-      <c r="C86" t="n">
-        <v>44</v>
-      </c>
-      <c r="D86" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>44985</v>
-      </c>
-      <c r="B87" t="n">
-        <v>41</v>
-      </c>
-      <c r="C87" t="n">
-        <v>49</v>
-      </c>
-      <c r="D87" t="n">
-        <v>41</v>
-      </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
@@ -3434,77 +3516,77 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C89" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D89" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C90" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D90" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
         <v>52</v>
       </c>
       <c r="C91" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D91" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C92" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
+        <v>49</v>
+      </c>
+      <c r="C93" t="n">
         <v>45</v>
       </c>
-      <c r="C93" t="n">
-        <v>46</v>
-      </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
@@ -3518,25 +3600,25 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C95" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D95" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C96" t="n">
         <v>46</v>
@@ -3546,95 +3628,95 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C97" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D97" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
+        <v>37</v>
+      </c>
+      <c r="C98" t="n">
+        <v>32</v>
+      </c>
+      <c r="D98" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B99" t="n">
+        <v>43</v>
+      </c>
+      <c r="C99" t="n">
         <v>40</v>
       </c>
-      <c r="C98" t="n">
-        <v>33</v>
-      </c>
-      <c r="D98" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="B99" t="n">
-        <v>38</v>
-      </c>
-      <c r="C99" t="n">
-        <v>41</v>
-      </c>
       <c r="D99" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C100" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D100" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C101" t="n">
         <v>53</v>
       </c>
       <c r="D101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C102" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D102" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C103" t="n">
         <v>49</v>
@@ -3644,77 +3726,77 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C104" t="n">
         <v>43</v>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C105" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D105" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C106" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C107" t="n">
         <v>26</v>
       </c>
       <c r="D107" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C108" t="n">
         <v>39</v>
       </c>
       <c r="D108" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B109" t="n">
@@ -3728,7 +3810,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B110" t="n">
@@ -3738,43 +3820,43 @@
         <v>29</v>
       </c>
       <c r="D110" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C111" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D111" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C112" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C113" t="n">
         <v>48</v>
@@ -3784,53 +3866,53 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C114" t="n">
         <v>48</v>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B115" t="n">
         <v>47</v>
       </c>
       <c r="C115" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D115" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B116" t="n">
+        <v>54</v>
+      </c>
+      <c r="C116" t="n">
+        <v>39</v>
+      </c>
+      <c r="D116" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>45869</v>
-      </c>
-      <c r="B116" t="n">
-        <v>50</v>
-      </c>
-      <c r="C116" t="n">
-        <v>40</v>
-      </c>
-      <c r="D116" t="n">
-        <v>6</v>
-      </c>
-    </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C117" t="n">
         <v>38</v>
@@ -3840,11 +3922,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C118" t="n">
         <v>30</v>
@@ -3854,53 +3936,53 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C119" t="n">
         <v>23</v>
       </c>
       <c r="D119" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C120" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D120" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C121" t="n">
         <v>26</v>
       </c>
       <c r="D121" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C122" t="n">
         <v>23</v>
@@ -3910,45 +3992,115 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C123" t="n">
         <v>30</v>
       </c>
       <c r="D123" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C124" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D124" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B125" t="n">
+        <v>36</v>
+      </c>
+      <c r="C125" t="n">
+        <v>47</v>
+      </c>
+      <c r="D125" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>41</v>
+      </c>
+      <c r="C126" t="n">
+        <v>46</v>
+      </c>
+      <c r="D126" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B127" t="n">
+        <v>41</v>
+      </c>
+      <c r="C127" t="n">
+        <v>43</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B128" t="n">
         <v>42</v>
       </c>
-      <c r="C125" t="n">
-        <v>44</v>
-      </c>
-      <c r="D125" t="n">
-        <v>12</v>
+      <c r="C128" t="n">
+        <v>35</v>
+      </c>
+      <c r="D128" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B129" t="n">
+        <v>40</v>
+      </c>
+      <c r="C129" t="n">
+        <v>25</v>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B130" t="n">
+        <v>33</v>
+      </c>
+      <c r="C130" t="n">
+        <v>22</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
